--- a/public/exports/29188955.xlsx
+++ b/public/exports/29188955.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:O50"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -24,55 +24,65 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ejerskab</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Primær registreret ejer</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Geografisk kommunekode</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t xml:space="preserve">Adresse</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t xml:space="preserve">Postnr.</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t xml:space="preserve">BFE-nummer</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bygningsnummer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Areal (m²)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">EM-nummer</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Energimærkningsfirma</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -91,53 +101,63 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Langeland Kommune</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">482</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Engdraget 10</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t xml:space="preserve">5900</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t xml:space="preserve">5490002</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H2">
+      <c r="J2">
         <v>1788</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -156,53 +176,63 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Langeland Kommune</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">482</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Engdraget 8</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t xml:space="preserve">5900</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t xml:space="preserve">9547826</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H3">
+      <c r="J3">
         <v>366</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -221,53 +251,63 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Langeland Kommune</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">482</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Hallinggade 25B</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">5932</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t xml:space="preserve">734158, 3074235</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="H4">
+      <c r="J4">
         <v>1650</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -286,53 +326,63 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnepladsen 39</t>
+          <t xml:space="preserve">Langeland Kommune</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">5900</t>
+          <t xml:space="preserve">482</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">734121, 5489406</t>
+          <t xml:space="preserve">Havnegade 2A</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="H5">
-        <v>1063</v>
+          <t xml:space="preserve">5935</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">734155, 8866627</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t xml:space="preserve">23</t>
+        </is>
+      </c>
+      <c r="J5">
+        <v>442</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -351,53 +401,63 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rue Mark 9</t>
+          <t xml:space="preserve">Langeland Kommune</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">5900</t>
+          <t xml:space="preserve">482</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">734136, 5490237</t>
+          <t xml:space="preserve">Havnegade 6A</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H6">
-        <v>593</v>
+          <t xml:space="preserve">5935</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">734155, 8866627</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t xml:space="preserve">42</t>
+        </is>
+      </c>
+      <c r="J6">
+        <v>264</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -416,53 +476,63 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandbakken 17</t>
+          <t xml:space="preserve">Langeland Kommune</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t xml:space="preserve">482</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Havnepladsen 39</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t xml:space="preserve">5900</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5490201</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H7">
-        <v>287</v>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">734121, 5489406</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="J7">
+        <v>1063</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -481,53 +551,63 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 25</t>
+          <t xml:space="preserve">Langeland Kommune</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t xml:space="preserve">482</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rue Mark 9</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t xml:space="preserve">5900</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5489077</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="H8">
-        <v>296</v>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">734136, 5490237</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J8">
+        <v>593</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -546,53 +626,63 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østerport 7</t>
+          <t xml:space="preserve">Langeland Kommune</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t xml:space="preserve">482</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Strandbakken 17</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t xml:space="preserve">5900</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5489577</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="H9">
-        <v>541</v>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5490201</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J9">
+        <v>287</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -611,55 +701,65 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 23</t>
+          <t xml:space="preserve">Langeland Kommune</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">5900</t>
+          <t xml:space="preserve">482</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">5489077</t>
+          <t xml:space="preserve">Værftsvej 59</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H10">
-        <v>560</v>
+          <t xml:space="preserve">5935</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">734202, 8866627</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">311425472</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+          <t xml:space="preserve">37</t>
+        </is>
+      </c>
+      <c r="J10">
+        <v>387</v>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2030-03-02</t>
-        </is>
-      </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mangler energimærke</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -676,55 +776,65 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stationsvej 6</t>
+          <t xml:space="preserve">Langeland Kommune</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5935</t>
+          <t xml:space="preserve">482</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3077138</t>
+          <t xml:space="preserve">Østergade 25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5489077</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H11">
-        <v>265</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311482534</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
-        </is>
+      <c r="J11">
+        <v>296</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mangler energimærke</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -741,55 +851,65 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vindeltorpvej 1</t>
+          <t xml:space="preserve">Langeland Kommune</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t xml:space="preserve">482</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Østerport 7</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t xml:space="preserve">5900</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3068632</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H12">
-        <v>1101</v>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5489577</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">311482524</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
-        </is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="J12">
+        <v>541</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mangler energimærke</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -806,53 +926,63 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langegade 30A</t>
+          <t xml:space="preserve">Langeland Kommune</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t xml:space="preserve">482</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Østergade 23</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t xml:space="preserve">5900</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8644450</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5489077</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H13">
-        <v>701</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311492859</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
-        </is>
+      <c r="J13">
+        <v>560</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-04</t>
+          <t xml:space="preserve">311425472</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2030-03-02</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -871,53 +1001,63 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langegade 30B</t>
+          <t xml:space="preserve">Langeland Kommune</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">5900</t>
+          <t xml:space="preserve">482</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">3075730</t>
+          <t xml:space="preserve">Stationsvej 6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H14">
-        <v>969</v>
+          <t xml:space="preserve">5935</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3077138</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">311492855</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="J14">
+        <v>265</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311482534</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2031-02-04</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2030-12-14</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -936,53 +1076,63 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langegade 30A</t>
+          <t xml:space="preserve">Langeland Kommune</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t xml:space="preserve">482</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vindeltorpvej 1</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
           <t xml:space="preserve">5900</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8644450</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="H15">
-        <v>2989</v>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3068632</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">311493489</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J15">
+        <v>1101</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-07</t>
+          <t xml:space="preserve">311482524</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2030-12-14</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1001,53 +1151,63 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ahlefeldtsgade 13</t>
+          <t xml:space="preserve">Langeland Kommune</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t xml:space="preserve">482</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Langegade 30A</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
           <t xml:space="preserve">5900</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5490955</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8644450</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H16">
-        <v>623</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311529196</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16">
+        <v>701</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311492859</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2031-02-19</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2031-02-04</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1066,53 +1226,63 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ahlefeldtsgade 13</t>
+          <t xml:space="preserve">Langeland Kommune</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t xml:space="preserve">482</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Langegade 30B</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
           <t xml:space="preserve">5900</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5490955</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="H17">
-        <v>373</v>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3075730</t>
+        </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529196</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J17">
+        <v>969</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311492855</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2031-02-19</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2031-02-04</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1131,53 +1301,63 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ahlefeldtsgade 13</t>
+          <t xml:space="preserve">Langeland Kommune</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t xml:space="preserve">482</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Langegade 30A</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t xml:space="preserve">5900</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5490955</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="H18">
-        <v>340</v>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8644450</t>
+        </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529186</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
-        </is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="J18">
+        <v>2989</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-22</t>
+          <t xml:space="preserve">311493489</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2031-02-07</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1196,53 +1376,63 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensvej 1A</t>
+          <t xml:space="preserve">Langeland Kommune</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t xml:space="preserve">482</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ahlefeldtsgade 13</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t xml:space="preserve">5900</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5489721</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="H19">
-        <v>828</v>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5490955</t>
+        </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529152</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J19">
+        <v>623</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311529196</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2031-05-07</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2031-02-19</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1261,53 +1451,63 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensvej 1</t>
+          <t xml:space="preserve">Langeland Kommune</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t xml:space="preserve">482</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ahlefeldtsgade 13</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t xml:space="preserve">5900</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5489721</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H20">
-        <v>5101</v>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5490955</t>
+        </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529147</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="J20">
+        <v>373</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311529196</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2031-05-25</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2031-02-19</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1326,53 +1526,63 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tullebølle Centret 2</t>
+          <t xml:space="preserve">Langeland Kommune</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5953</t>
+          <t xml:space="preserve">482</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">302908, 302909</t>
+          <t xml:space="preserve">Ahlefeldtsgade 13</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H21">
-        <v>4625</v>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5490955</t>
+        </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">311542244</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="J21">
+        <v>340</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311529186</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2031-08-20</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2031-02-22</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1391,53 +1601,63 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tværvej 15</t>
+          <t xml:space="preserve">Langeland Kommune</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">5932</t>
+          <t xml:space="preserve">482</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">3074374</t>
+          <t xml:space="preserve">Fredensvej 1A</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H22">
-        <v>308</v>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5489721</t>
+        </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">311542539</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="J22">
+        <v>828</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311529152</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2031-08-23</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2031-05-07</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1456,53 +1676,63 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stigtehaven 6</t>
+          <t xml:space="preserve">Langeland Kommune</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">5953</t>
+          <t xml:space="preserve">482</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">9369230</t>
+          <t xml:space="preserve">Fredensvej 1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5489721</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H23">
-        <v>1499</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311545477</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
+      <c r="J23">
+        <v>5101</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311529147</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2031-09-02</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2031-05-25</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1521,53 +1751,63 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensvej 1B</t>
+          <t xml:space="preserve">Langeland Kommune</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">5900</t>
+          <t xml:space="preserve">482</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">5489721</t>
+          <t xml:space="preserve">Tullebølle Centret 2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="H24">
-        <v>347</v>
+          <t xml:space="preserve">5953</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">302908, 302909</t>
+        </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549943</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J24">
+        <v>4625</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311542244</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2031-09-22</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2031-08-20</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1586,53 +1826,63 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hinestien 1</t>
+          <t xml:space="preserve">Langeland Kommune</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5900</t>
+          <t xml:space="preserve">482</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">7099564</t>
+          <t xml:space="preserve">Tværvej 15</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
+          <t xml:space="preserve">5932</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3074374</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H25">
-        <v>354</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311563855</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
+      <c r="J25">
+        <v>308</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311542539</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2031-09-27</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2031-08-23</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1651,53 +1901,63 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrebro 75</t>
+          <t xml:space="preserve">Langeland Kommune</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5900</t>
+          <t xml:space="preserve">482</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">100040956</t>
+          <t xml:space="preserve">Stigtehaven 6</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
+          <t xml:space="preserve">5953</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9369230</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H26">
-        <v>316</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311551653</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
+      <c r="J26">
+        <v>1499</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311545477</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2031-09-29</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2031-09-02</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1716,53 +1976,63 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnegade 118</t>
+          <t xml:space="preserve">Langeland Kommune</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t xml:space="preserve">482</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fredensvej 1B</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
           <t xml:space="preserve">5900</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100062527</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="H27">
-        <v>897</v>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5489721</t>
+        </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311563862</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="J27">
+        <v>347</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311549943</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2031-11-09</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2031-09-22</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1781,53 +2051,63 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnegade 118</t>
+          <t xml:space="preserve">Langeland Kommune</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t xml:space="preserve">482</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hinestien 1</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
           <t xml:space="preserve">5900</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100062527</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7099564</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H28">
-        <v>3054</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311563858</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
+      <c r="J28">
+        <v>354</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311563855</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2031-11-11</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2031-09-27</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1846,53 +2126,63 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnegade 7</t>
+          <t xml:space="preserve">Langeland Kommune</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
+          <t xml:space="preserve">482</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nørrebro 75</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
           <t xml:space="preserve">5900</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5489428</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100040956</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H29">
-        <v>866</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311568384</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="J29">
+        <v>316</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-16</t>
+          <t xml:space="preserve">311551653</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2031-09-29</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1911,53 +2201,63 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 55</t>
+          <t xml:space="preserve">Langeland Kommune</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">5932</t>
+          <t xml:space="preserve">482</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">301970, 301971</t>
+          <t xml:space="preserve">Havnegade 118</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H30">
-        <v>2083</v>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100062527</t>
+        </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568316</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="J30">
+        <v>897</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311563862</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2031-12-16</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2031-11-09</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1976,53 +2276,63 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jens Winthers Vej 12</t>
+          <t xml:space="preserve">Langeland Kommune</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t xml:space="preserve">482</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Havnegade 118</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
           <t xml:space="preserve">5900</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7099542</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100062527</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H31">
-        <v>988</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311571524</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
+      <c r="J31">
+        <v>3054</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311563858</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2032-01-10</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2031-11-11</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2041,53 +2351,63 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jens Winthers Vej 12</t>
+          <t xml:space="preserve">Langeland Kommune</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
+          <t xml:space="preserve">482</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Havnegade 7</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
           <t xml:space="preserve">5900</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7099542</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="H32">
-        <v>886</v>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5489428</t>
+        </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311571525</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
-        </is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J32">
+        <v>866</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-10</t>
+          <t xml:space="preserve">311568384</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2031-12-16</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2106,53 +2426,63 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 64</t>
+          <t xml:space="preserve">Langeland Kommune</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t xml:space="preserve">482</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hovedgaden 55</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
           <t xml:space="preserve">5932</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3074196</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">301970, 301971</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H33">
-        <v>2602</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311580361</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
+      <c r="J33">
+        <v>2083</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311568316</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2032-02-22</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2031-12-16</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2171,53 +2501,63 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 64</t>
+          <t xml:space="preserve">Langeland Kommune</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">5932</t>
+          <t xml:space="preserve">482</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">3074196</t>
+          <t xml:space="preserve">Jens Winthers Vej 12</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="H34">
-        <v>352</v>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7099542</t>
+        </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311580361</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J34">
+        <v>988</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311571524</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2032-02-22</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2032-01-10</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2236,53 +2576,63 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 64</t>
+          <t xml:space="preserve">Langeland Kommune</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">5932</t>
+          <t xml:space="preserve">482</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">3074196</t>
+          <t xml:space="preserve">Jens Winthers Vej 12</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="H35">
-        <v>586</v>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7099542</t>
+        </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311580361</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="J35">
+        <v>886</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311571525</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2032-02-22</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2032-01-10</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2301,53 +2651,63 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Langeland Kommune</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">482</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t xml:space="preserve">Hovedgaden 64</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t xml:space="preserve">5932</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t xml:space="preserve">3074196</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8</t>
-        </is>
-      </c>
-      <c r="H36">
-        <v>395</v>
-      </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311580360</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J36">
+        <v>2602</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311580361</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-02-22</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2366,53 +2726,63 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørstedsgade 16</t>
+          <t xml:space="preserve">Langeland Kommune</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">5900</t>
+          <t xml:space="preserve">482</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">5488951</t>
+          <t xml:space="preserve">Hovedgaden 64</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H37">
-        <v>668</v>
+          <t xml:space="preserve">5932</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3074196</t>
+        </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311584100</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="J37">
+        <v>352</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311580361</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2032-03-10</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2032-02-22</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2431,53 +2801,63 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mjølbyvej 8</t>
+          <t xml:space="preserve">Langeland Kommune</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">5900</t>
+          <t xml:space="preserve">482</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">5490140</t>
+          <t xml:space="preserve">Hovedgaden 64</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H38">
-        <v>852</v>
+          <t xml:space="preserve">5932</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3074196</t>
+        </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311585659</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="J38">
+        <v>586</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311580361</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2032-03-16</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2032-02-22</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2496,53 +2876,63 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnegade 2A</t>
+          <t xml:space="preserve">Langeland Kommune</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">5935</t>
+          <t xml:space="preserve">482</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">734155, 8866627</t>
+          <t xml:space="preserve">Hovedgaden 64</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
-        </is>
-      </c>
-      <c r="H39">
-        <v>442</v>
+          <t xml:space="preserve">5932</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3074196</t>
+        </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311585991</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="J39">
+        <v>395</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-17</t>
+          <t xml:space="preserve">311580360</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2032-02-22</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2561,53 +2951,63 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnegade 6A</t>
+          <t xml:space="preserve">Langeland Kommune</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">5935</t>
+          <t xml:space="preserve">482</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">734155, 8866627</t>
+          <t xml:space="preserve">Ørstedsgade 16</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
-        </is>
-      </c>
-      <c r="H40">
-        <v>264</v>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5488951</t>
+        </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311585991</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J40">
+        <v>668</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-17</t>
+          <t xml:space="preserve">311584100</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2032-03-10</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2626,53 +3026,63 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Værftsvej 59</t>
+          <t xml:space="preserve">Langeland Kommune</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">5935</t>
+          <t xml:space="preserve">482</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">734202, 8866627</t>
+          <t xml:space="preserve">Mjølbyvej 8</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
-        </is>
-      </c>
-      <c r="H41">
-        <v>387</v>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5490140</t>
+        </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311585991</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J41">
+        <v>852</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-17</t>
+          <t xml:space="preserve">311585659</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2032-03-16</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2691,53 +3101,63 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t xml:space="preserve">Langeland Kommune</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">482</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t xml:space="preserve">Vindeltorpvej 1A</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t xml:space="preserve">5900</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t xml:space="preserve">3068632</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H42">
+      <c r="J42">
         <v>393</v>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t xml:space="preserve">311586376</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-18</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2756,53 +3176,63 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t xml:space="preserve">Langeland Kommune</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">482</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t xml:space="preserve">Spodsbjergvej 129</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t xml:space="preserve">5900</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t xml:space="preserve">5490100</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H43">
+      <c r="J43">
         <v>2067</v>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t xml:space="preserve">311586784</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-21</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2821,53 +3251,63 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Langeland Kommune</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">482</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t xml:space="preserve">Havnegade 118B</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t xml:space="preserve">5900</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t xml:space="preserve">5490887</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="H44">
+      <c r="J44">
         <v>1786</v>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t xml:space="preserve">311587824</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-24</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2886,53 +3326,63 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t xml:space="preserve">Langeland Kommune</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">482</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t xml:space="preserve">Spodsbjergvej 52B</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t xml:space="preserve">5900</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t xml:space="preserve">9547828</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H45">
+      <c r="J45">
         <v>305</v>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t xml:space="preserve">311588491</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-28</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2951,53 +3401,63 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t xml:space="preserve">Langeland Kommune</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">482</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t xml:space="preserve">Spodsbjergvej 201</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t xml:space="preserve">5900</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t xml:space="preserve">302956</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H46">
+      <c r="J46">
         <v>387</v>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t xml:space="preserve">311589021</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-29</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3016,53 +3476,63 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t xml:space="preserve">Langeland Kommune</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">482</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t xml:space="preserve">Spodsbjergvej 201</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t xml:space="preserve">5900</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t xml:space="preserve">302956</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="H47">
+      <c r="J47">
         <v>1011</v>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t xml:space="preserve">311589021</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-29</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3081,53 +3551,63 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t xml:space="preserve">Langeland Kommune</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">482</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nordre Landevej 65</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t xml:space="preserve">5900</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t xml:space="preserve">3068305</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H48">
+      <c r="J48">
         <v>254</v>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t xml:space="preserve">311592796</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-04-12</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3146,53 +3626,63 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t xml:space="preserve">Langeland Kommune</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">482</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nordre Landevej 65</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t xml:space="preserve">5900</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t xml:space="preserve">3068305</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H49">
+      <c r="J49">
         <v>548</v>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t xml:space="preserve">311592796</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-04-12</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3211,59 +3701,69 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t xml:space="preserve">Langeland Kommune</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">482</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t xml:space="preserve">Snødevej 138</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t xml:space="preserve">5953</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t xml:space="preserve">3069065</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H50">
+      <c r="J50">
         <v>1663</v>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t xml:space="preserve">311592782</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-04-12</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M50"/>
+  <autoFilter ref="A1:O50"/>
 </worksheet>
 </file>
--- a/public/exports/29188955.xlsx
+++ b/public/exports/29188955.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
